--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_LEAUNF-CSTD-1-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_LEAUNF-CSTD-1-00-A-C0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\設計成果物_MET\MCU-DT\02.Design\06.FF2\A1.要件\BEV3CDCMET-2607_H_LEAUNF\01.パラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3ECA37-5937-43BF-A56B-99A81E95A821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB1B712A-26E5-4B76-B875-42DBCE709707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認）" sheetId="14" r:id="rId1"/>
@@ -471,133 +471,6 @@
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">電源状態は、各入力/出力信号の電源状態を記載する。
-ALERT_CH_XXXの出力は、機能の電源状態を記載するので注意。
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">リモート送信条件成立：IG ON 且つ PTS ONが15[s]以上
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">IG ON 且つ ST OFF
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>IG ON</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">IG OFF 且つ IG OFF後25[m]未満
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">IG OFF
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">IG ON 又は IG OFF後25[m]未満
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0700-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>+B ON 又は ACC ON</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="B79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000009000000}">
       <text>
         <r>
@@ -730,7 +603,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="277">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -1689,10 +1562,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>UNKNOWN</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>１．本書の目的</t>
     <rPh sb="2" eb="4">
       <t>ホンショ</t>
@@ -1864,10 +1733,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>REQ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">対象となるTMC Specならびに分析した結果で決定されるAlert Channel情報について記載する。
 </t>
@@ -1983,10 +1848,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Table Type</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>対象のTMC Specを分析した際の中間成果物。参考情報として記載。メンテナンス対象外。</t>
     <rPh sb="0" eb="2">
       <t>タイショウ</t>
@@ -2019,14 +1880,6 @@
   </si>
   <si>
     <t>入力</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VOM</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2063,10 +1916,6 @@
   <si>
     <t>0b/
 1b</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2205,10 +2054,6 @@
   </si>
   <si>
     <t>Config_IF</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Vehicle Operation Mode</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2778,17 +2623,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>PLG1G14</t>
-  </si>
-  <si>
-    <t>PLG1G14</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PLG1G14_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>0b</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2807,15 +2641,7 @@
     <t>Index</t>
   </si>
   <si>
-    <t>ALERT_CH_H_LEAUNF_PD_PWC</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ALERT_CH_H_LEAUNF_PD_EHV</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SILUAPWC_SIG</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2843,16 +2669,7 @@
     <t>*b</t>
   </si>
   <si>
-    <t>H_LEAUNF-CSTD-0-MEF01-REQ02/
--</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>REQ02</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2991,13 +2808,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>仕様情報学習等未完警告 PD_PWC判定</t>
-    <rPh sb="18" eb="20">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>仕様情報学習等未完警告 PD_EHV判定</t>
     <rPh sb="18" eb="20">
       <t>ハンテイ</t>
@@ -3105,9 +2915,6 @@
   </si>
   <si>
     <t>&lt;DT検討印&gt;</t>
-  </si>
-  <si>
-    <t>DENSO TECHNO PHIL. INC</t>
   </si>
   <si>
     <t>1.3.0</t>
@@ -3241,6 +3048,33 @@
     <rPh sb="83" eb="85">
       <t>サクジョ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.5.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BEV FF2対応
+[Reference]シート
+・キャプチャ更新（PD_PWC判定削除）</t>
+    <rPh sb="31" eb="33">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KSE中島寧花</t>
+    <rPh sb="3" eb="7">
+      <t>ナカジマネイハナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(株)カーネル・ソフト・エンジニアリング</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4652,7 +4486,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5343,6 +5177,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" xfId="2" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="27" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5520,9 +5357,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5531,6 +5365,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5623,6 +5460,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>47554</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>28504</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3419EEB-0D07-4E42-2850-552C89558A8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="7896225"/>
+          <a:ext cx="571429" cy="571429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6417,7 +6303,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -6429,8 +6315,8 @@
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>397328</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>44524</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>101674</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6611,308 +6497,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>493058</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>3</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1632857</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>148882</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="線吹き出し 1 (枠付き) 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6523744" y="13563603"/>
-          <a:ext cx="5178399" cy="638736"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 42429"/>
-            <a:gd name="adj2" fmla="val -3670"/>
-            <a:gd name="adj3" fmla="val -49219"/>
-            <a:gd name="adj4" fmla="val -22728"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>途絶時は通信ソフト側で保持する信号値をそのまま使用するため、</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>未受信ビットのみを参照する</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1089214</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>35861</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>80683</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>35858</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="線吹き出し 1 (枠付き) 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00001D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1698814" y="13868402"/>
-          <a:ext cx="3276598" cy="681315"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -3100"/>
-            <a:gd name="adj2" fmla="val 49057"/>
-            <a:gd name="adj3" fmla="val -25796"/>
-            <a:gd name="adj4" fmla="val 60842"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>電源状態</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>(VOM)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>は判定条件に含めない</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>・</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>IG</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>は通信状態</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>未受信</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>に含まれる</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -7393,8 +6977,8 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>434068</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>1647826</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7691,8 +7275,8 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>554182</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>581025</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7849,8 +7433,8 @@
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>619126</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8004,8 +7588,8 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>536121</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>1638300</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8070,8 +7654,8 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>188646</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>131154</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>140679</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8159,8 +7743,8 @@
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>1657350</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8225,8 +7809,8 @@
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>88929</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>50829</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8314,8 +7898,8 @@
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>672193</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>647700</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9167,8 +8751,8 @@
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>455557</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>173117</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1667</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9920,91 +9504,91 @@
       <c r="AN8" s="219"/>
     </row>
     <row r="9" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A9" s="235" t="str">
+      <c r="A9" s="236" t="str">
         <f ca="1">MID(CELL("filename",A1), FIND("[",CELL("filename",A1))+1, FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-6)</f>
         <v>alert_H_LEAUNF-CSTD-1-00-A-C0</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="236"/>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
-      <c r="T9" s="236"/>
-      <c r="U9" s="236"/>
-      <c r="V9" s="236"/>
-      <c r="W9" s="236"/>
-      <c r="X9" s="236"/>
-      <c r="Y9" s="236"/>
-      <c r="Z9" s="236"/>
-      <c r="AA9" s="236"/>
-      <c r="AB9" s="236"/>
-      <c r="AC9" s="236"/>
-      <c r="AD9" s="236"/>
-      <c r="AE9" s="236"/>
-      <c r="AF9" s="236"/>
-      <c r="AG9" s="236"/>
-      <c r="AH9" s="236"/>
-      <c r="AI9" s="236"/>
-      <c r="AJ9" s="236"/>
-      <c r="AK9" s="236"/>
-      <c r="AL9" s="236"/>
-      <c r="AM9" s="236"/>
-      <c r="AN9" s="237"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="237"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="237"/>
+      <c r="K9" s="237"/>
+      <c r="L9" s="237"/>
+      <c r="M9" s="237"/>
+      <c r="N9" s="237"/>
+      <c r="O9" s="237"/>
+      <c r="P9" s="237"/>
+      <c r="Q9" s="237"/>
+      <c r="R9" s="237"/>
+      <c r="S9" s="237"/>
+      <c r="T9" s="237"/>
+      <c r="U9" s="237"/>
+      <c r="V9" s="237"/>
+      <c r="W9" s="237"/>
+      <c r="X9" s="237"/>
+      <c r="Y9" s="237"/>
+      <c r="Z9" s="237"/>
+      <c r="AA9" s="237"/>
+      <c r="AB9" s="237"/>
+      <c r="AC9" s="237"/>
+      <c r="AD9" s="237"/>
+      <c r="AE9" s="237"/>
+      <c r="AF9" s="237"/>
+      <c r="AG9" s="237"/>
+      <c r="AH9" s="237"/>
+      <c r="AI9" s="237"/>
+      <c r="AJ9" s="237"/>
+      <c r="AK9" s="237"/>
+      <c r="AL9" s="237"/>
+      <c r="AM9" s="237"/>
+      <c r="AN9" s="238"/>
     </row>
     <row r="10" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A10" s="235"/>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="236"/>
-      <c r="U10" s="236"/>
-      <c r="V10" s="236"/>
-      <c r="W10" s="236"/>
-      <c r="X10" s="236"/>
-      <c r="Y10" s="236"/>
-      <c r="Z10" s="236"/>
-      <c r="AA10" s="236"/>
-      <c r="AB10" s="236"/>
-      <c r="AC10" s="236"/>
-      <c r="AD10" s="236"/>
-      <c r="AE10" s="236"/>
-      <c r="AF10" s="236"/>
-      <c r="AG10" s="236"/>
-      <c r="AH10" s="236"/>
-      <c r="AI10" s="236"/>
-      <c r="AJ10" s="236"/>
-      <c r="AK10" s="236"/>
-      <c r="AL10" s="236"/>
-      <c r="AM10" s="236"/>
-      <c r="AN10" s="237"/>
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="237"/>
+      <c r="J10" s="237"/>
+      <c r="K10" s="237"/>
+      <c r="L10" s="237"/>
+      <c r="M10" s="237"/>
+      <c r="N10" s="237"/>
+      <c r="O10" s="237"/>
+      <c r="P10" s="237"/>
+      <c r="Q10" s="237"/>
+      <c r="R10" s="237"/>
+      <c r="S10" s="237"/>
+      <c r="T10" s="237"/>
+      <c r="U10" s="237"/>
+      <c r="V10" s="237"/>
+      <c r="W10" s="237"/>
+      <c r="X10" s="237"/>
+      <c r="Y10" s="237"/>
+      <c r="Z10" s="237"/>
+      <c r="AA10" s="237"/>
+      <c r="AB10" s="237"/>
+      <c r="AC10" s="237"/>
+      <c r="AD10" s="237"/>
+      <c r="AE10" s="237"/>
+      <c r="AF10" s="237"/>
+      <c r="AG10" s="237"/>
+      <c r="AH10" s="237"/>
+      <c r="AI10" s="237"/>
+      <c r="AJ10" s="237"/>
+      <c r="AK10" s="237"/>
+      <c r="AL10" s="237"/>
+      <c r="AM10" s="237"/>
+      <c r="AN10" s="238"/>
     </row>
     <row r="11" spans="1:40" ht="13.5" customHeight="1">
       <c r="A11" s="217"/>
@@ -10662,7 +10246,7 @@
       <c r="W26" s="218"/>
       <c r="X26" s="218"/>
       <c r="Y26" s="220" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="Z26" s="218"/>
       <c r="AA26" s="218"/>
@@ -10705,27 +10289,27 @@
       <c r="V27" s="218"/>
       <c r="W27" s="218"/>
       <c r="X27" s="218"/>
-      <c r="Y27" s="232" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z27" s="233"/>
-      <c r="AA27" s="233"/>
-      <c r="AB27" s="233"/>
-      <c r="AC27" s="234"/>
-      <c r="AD27" s="232" t="s">
-        <v>268</v>
-      </c>
-      <c r="AE27" s="233"/>
-      <c r="AF27" s="233"/>
-      <c r="AG27" s="233"/>
-      <c r="AH27" s="234"/>
-      <c r="AI27" s="238" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ27" s="233"/>
-      <c r="AK27" s="233"/>
-      <c r="AL27" s="233"/>
-      <c r="AM27" s="234"/>
+      <c r="Y27" s="233" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z27" s="234"/>
+      <c r="AA27" s="234"/>
+      <c r="AB27" s="234"/>
+      <c r="AC27" s="235"/>
+      <c r="AD27" s="233" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE27" s="234"/>
+      <c r="AF27" s="234"/>
+      <c r="AG27" s="234"/>
+      <c r="AH27" s="235"/>
+      <c r="AI27" s="239" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ27" s="234"/>
+      <c r="AK27" s="234"/>
+      <c r="AL27" s="234"/>
+      <c r="AM27" s="235"/>
       <c r="AN27" s="219"/>
     </row>
     <row r="28" spans="1:40" ht="13.5" customHeight="1">
@@ -10840,14 +10424,14 @@
       <c r="Y30" s="217"/>
       <c r="Z30" s="218"/>
       <c r="AA30" s="223" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="AB30" s="218"/>
       <c r="AC30" s="219"/>
       <c r="AD30" s="217"/>
       <c r="AE30" s="218"/>
       <c r="AF30" s="223" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="AG30" s="218"/>
       <c r="AH30" s="219"/>
@@ -11010,7 +10594,7 @@
       <c r="W34" s="218"/>
       <c r="X34" s="218"/>
       <c r="Y34" s="220" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="Z34" s="218"/>
       <c r="AA34" s="218"/>
@@ -11053,27 +10637,27 @@
       <c r="V35" s="218"/>
       <c r="W35" s="218"/>
       <c r="X35" s="218"/>
-      <c r="Y35" s="232" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z35" s="233"/>
-      <c r="AA35" s="233"/>
-      <c r="AB35" s="233"/>
-      <c r="AC35" s="234"/>
-      <c r="AD35" s="232" t="s">
-        <v>268</v>
-      </c>
-      <c r="AE35" s="233"/>
-      <c r="AF35" s="233"/>
-      <c r="AG35" s="233"/>
-      <c r="AH35" s="234"/>
-      <c r="AI35" s="238" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ35" s="233"/>
-      <c r="AK35" s="233"/>
-      <c r="AL35" s="233"/>
-      <c r="AM35" s="234"/>
+      <c r="Y35" s="233" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z35" s="234"/>
+      <c r="AA35" s="234"/>
+      <c r="AB35" s="234"/>
+      <c r="AC35" s="235"/>
+      <c r="AD35" s="233" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE35" s="234"/>
+      <c r="AF35" s="234"/>
+      <c r="AG35" s="234"/>
+      <c r="AH35" s="235"/>
+      <c r="AI35" s="239" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ35" s="234"/>
+      <c r="AK35" s="234"/>
+      <c r="AL35" s="234"/>
+      <c r="AM35" s="235"/>
       <c r="AN35" s="219"/>
     </row>
     <row r="36" spans="1:40" ht="13.5" customHeight="1">
@@ -11188,21 +10772,21 @@
       <c r="Y38" s="217"/>
       <c r="Z38" s="218"/>
       <c r="AA38" s="223" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="AB38" s="218"/>
       <c r="AC38" s="219"/>
       <c r="AD38" s="217"/>
       <c r="AE38" s="218"/>
       <c r="AF38" s="223" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="AG38" s="218"/>
       <c r="AH38" s="219"/>
       <c r="AI38" s="217"/>
       <c r="AJ38" s="218"/>
       <c r="AK38" s="223" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="AL38" s="218"/>
       <c r="AM38" s="219"/>
@@ -11359,8 +10943,8 @@
       <c r="V42" s="218"/>
       <c r="W42" s="218"/>
       <c r="X42" s="218"/>
-      <c r="Y42" s="220" t="s">
-        <v>275</v>
+      <c r="Y42" s="160" t="s">
+        <v>276</v>
       </c>
       <c r="Z42" s="218"/>
       <c r="AA42" s="218"/>
@@ -11403,27 +10987,27 @@
       <c r="V43" s="218"/>
       <c r="W43" s="218"/>
       <c r="X43" s="218"/>
-      <c r="Y43" s="232" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z43" s="233"/>
-      <c r="AA43" s="233"/>
-      <c r="AB43" s="233"/>
-      <c r="AC43" s="234"/>
-      <c r="AD43" s="232" t="s">
-        <v>268</v>
-      </c>
-      <c r="AE43" s="233"/>
-      <c r="AF43" s="233"/>
-      <c r="AG43" s="233"/>
-      <c r="AH43" s="234"/>
-      <c r="AI43" s="232" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ43" s="233"/>
-      <c r="AK43" s="233"/>
-      <c r="AL43" s="233"/>
-      <c r="AM43" s="234"/>
+      <c r="Y43" s="233" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z43" s="234"/>
+      <c r="AA43" s="234"/>
+      <c r="AB43" s="234"/>
+      <c r="AC43" s="235"/>
+      <c r="AD43" s="233" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE43" s="234"/>
+      <c r="AF43" s="234"/>
+      <c r="AG43" s="234"/>
+      <c r="AH43" s="235"/>
+      <c r="AI43" s="233" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ43" s="234"/>
+      <c r="AK43" s="234"/>
+      <c r="AL43" s="234"/>
+      <c r="AM43" s="235"/>
       <c r="AN43" s="219"/>
     </row>
     <row r="44" spans="1:40" ht="13.5" customHeight="1">
@@ -11451,17 +11035,17 @@
       <c r="V44" s="218"/>
       <c r="W44" s="218"/>
       <c r="X44" s="218"/>
-      <c r="Y44" s="221"/>
+      <c r="Y44" s="213"/>
       <c r="Z44" s="214"/>
       <c r="AA44" s="214"/>
       <c r="AB44" s="214"/>
       <c r="AC44" s="215"/>
-      <c r="AD44" s="221"/>
+      <c r="AD44" s="213"/>
       <c r="AE44" s="214"/>
       <c r="AF44" s="214"/>
       <c r="AG44" s="214"/>
       <c r="AH44" s="215"/>
-      <c r="AI44" s="221"/>
+      <c r="AI44" s="213"/>
       <c r="AJ44" s="214"/>
       <c r="AK44" s="214"/>
       <c r="AL44" s="214"/>
@@ -11494,19 +11078,19 @@
       <c r="W45" s="218"/>
       <c r="X45" s="218"/>
       <c r="Y45" s="217"/>
-      <c r="Z45" s="222"/>
-      <c r="AA45" s="218"/>
-      <c r="AB45" s="218"/>
+      <c r="Z45" s="232"/>
+      <c r="AA45" s="232"/>
+      <c r="AB45" s="232"/>
       <c r="AC45" s="219"/>
       <c r="AD45" s="217"/>
-      <c r="AE45" s="222"/>
-      <c r="AF45" s="218"/>
-      <c r="AG45" s="218"/>
+      <c r="AE45" s="232"/>
+      <c r="AF45" s="232"/>
+      <c r="AG45" s="232"/>
       <c r="AH45" s="219"/>
       <c r="AI45" s="217"/>
-      <c r="AJ45" s="222"/>
-      <c r="AK45" s="218"/>
-      <c r="AL45" s="218"/>
+      <c r="AJ45" s="232"/>
+      <c r="AK45" s="232"/>
+      <c r="AL45" s="232"/>
       <c r="AM45" s="219"/>
       <c r="AN45" s="219"/>
     </row>
@@ -11536,19 +11120,19 @@
       <c r="W46" s="218"/>
       <c r="X46" s="218"/>
       <c r="Y46" s="217"/>
-      <c r="Z46" s="218"/>
-      <c r="AA46" s="222"/>
-      <c r="AB46" s="218"/>
+      <c r="Z46" s="232"/>
+      <c r="AA46" s="232"/>
+      <c r="AB46" s="232"/>
       <c r="AC46" s="219"/>
       <c r="AD46" s="217"/>
-      <c r="AE46" s="218"/>
-      <c r="AF46" s="222"/>
-      <c r="AG46" s="218"/>
+      <c r="AE46" s="232"/>
+      <c r="AF46" s="232"/>
+      <c r="AG46" s="232"/>
       <c r="AH46" s="219"/>
       <c r="AI46" s="217"/>
-      <c r="AJ46" s="218"/>
-      <c r="AK46" s="222"/>
-      <c r="AL46" s="218"/>
+      <c r="AJ46" s="232"/>
+      <c r="AK46" s="232"/>
+      <c r="AL46" s="232"/>
       <c r="AM46" s="219"/>
       <c r="AN46" s="219"/>
     </row>
@@ -11578,19 +11162,19 @@
       <c r="W47" s="218"/>
       <c r="X47" s="218"/>
       <c r="Y47" s="217"/>
-      <c r="Z47" s="218"/>
-      <c r="AA47" s="218"/>
-      <c r="AB47" s="222"/>
+      <c r="Z47" s="232"/>
+      <c r="AA47" s="232"/>
+      <c r="AB47" s="232"/>
       <c r="AC47" s="219"/>
       <c r="AD47" s="217"/>
-      <c r="AE47" s="218"/>
-      <c r="AF47" s="218"/>
-      <c r="AG47" s="222"/>
+      <c r="AE47" s="232"/>
+      <c r="AF47" s="232"/>
+      <c r="AG47" s="232"/>
       <c r="AH47" s="219"/>
       <c r="AI47" s="217"/>
-      <c r="AJ47" s="218"/>
-      <c r="AK47" s="218"/>
-      <c r="AL47" s="222"/>
+      <c r="AJ47" s="232"/>
+      <c r="AK47" s="232"/>
+      <c r="AL47" s="232"/>
       <c r="AM47" s="219"/>
       <c r="AN47" s="219"/>
     </row>
@@ -11623,17 +11207,17 @@
       <c r="Z48" s="225"/>
       <c r="AA48" s="225"/>
       <c r="AB48" s="225"/>
-      <c r="AC48" s="227"/>
+      <c r="AC48" s="226"/>
       <c r="AD48" s="224"/>
       <c r="AE48" s="225"/>
       <c r="AF48" s="225"/>
       <c r="AG48" s="225"/>
-      <c r="AH48" s="227"/>
+      <c r="AH48" s="226"/>
       <c r="AI48" s="224"/>
       <c r="AJ48" s="225"/>
       <c r="AK48" s="225"/>
       <c r="AL48" s="225"/>
-      <c r="AM48" s="227"/>
+      <c r="AM48" s="226"/>
       <c r="AN48" s="219"/>
     </row>
     <row r="49" spans="1:40" ht="13.5" customHeight="1">
@@ -11698,13 +11282,14 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X14"/>
+  <dimension ref="B2:X15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -11723,18 +11308,18 @@
       <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="239" t="s">
+      <c r="I2" s="240" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="239"/>
-      <c r="P2" s="239"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="239"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="M2" s="240"/>
+      <c r="N2" s="240"/>
+      <c r="O2" s="240"/>
+      <c r="P2" s="240"/>
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="7"/>
@@ -11745,26 +11330,26 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="H3" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="I3" s="240" t="s">
-        <v>191</v>
-      </c>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
-      <c r="M3" s="241"/>
-      <c r="N3" s="241"/>
-      <c r="O3" s="241"/>
-      <c r="P3" s="241"/>
-      <c r="Q3" s="241"/>
-      <c r="R3" s="241"/>
+        <v>185</v>
+      </c>
+      <c r="I3" s="241" t="s">
+        <v>184</v>
+      </c>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="M3" s="242"/>
+      <c r="N3" s="242"/>
+      <c r="O3" s="242"/>
+      <c r="P3" s="242"/>
+      <c r="Q3" s="242"/>
+      <c r="R3" s="242"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="25" t="str">
-        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C16,"Ver.",H4:H5)</f>
         <v>1.3.0</v>
       </c>
       <c r="F4" s="7"/>
@@ -11778,44 +11363,44 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="H5" s="12">
-        <f>MAX(B9:B15)</f>
+        <f>MAX(B9:B16)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="245" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="246"/>
-      <c r="E7" s="247" t="s">
+      <c r="C7" s="246" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="247"/>
+      <c r="E7" s="248" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="247"/>
-      <c r="G7" s="248" t="s">
+      <c r="F7" s="248"/>
+      <c r="G7" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="249" t="s">
+      <c r="H7" s="249"/>
+      <c r="I7" s="249"/>
+      <c r="J7" s="249"/>
+      <c r="K7" s="249"/>
+      <c r="L7" s="249"/>
+      <c r="M7" s="250" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="249"/>
-      <c r="O7" s="249"/>
-      <c r="P7" s="249"/>
-      <c r="Q7" s="249"/>
-      <c r="R7" s="250"/>
-      <c r="S7" s="242" t="s">
-        <v>278</v>
-      </c>
-      <c r="T7" s="243"/>
-      <c r="U7" s="243"/>
-      <c r="V7" s="243"/>
-      <c r="W7" s="243"/>
-      <c r="X7" s="244"/>
+      <c r="N7" s="250"/>
+      <c r="O7" s="250"/>
+      <c r="P7" s="250"/>
+      <c r="Q7" s="250"/>
+      <c r="R7" s="251"/>
+      <c r="S7" s="243" t="s">
+        <v>262</v>
+      </c>
+      <c r="T7" s="244"/>
+      <c r="U7" s="244"/>
+      <c r="V7" s="244"/>
+      <c r="W7" s="244"/>
+      <c r="X7" s="245"/>
     </row>
     <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="10" t="s">
@@ -11870,7 +11455,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="228" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="T8" s="17" t="s">
         <v>7</v>
@@ -11903,7 +11488,7 @@
         <v>31</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>31</v>
@@ -11936,7 +11521,7 @@
         <v>31</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="R9" s="210">
         <v>44162</v>
@@ -11962,20 +11547,20 @@
     </row>
     <row r="10" spans="2:24" ht="67.5">
       <c r="B10" s="10">
-        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B15" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D10" s="211" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>31</v>
@@ -12008,7 +11593,7 @@
         <v>31</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="R10" s="212">
         <v>44279</v>
@@ -12038,16 +11623,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D11" s="211" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>31</v>
@@ -12080,7 +11665,7 @@
         <v>31</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="R11" s="212">
         <v>44575</v>
@@ -12110,16 +11695,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="D12" s="211" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>31</v>
@@ -12170,7 +11755,7 @@
         <v>31</v>
       </c>
       <c r="W12" s="14" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="X12" s="212">
         <v>45308</v>
@@ -12178,16 +11763,16 @@
     </row>
     <row r="13" spans="2:24" ht="81">
       <c r="C13" s="2" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D13" s="211" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>31</v>
@@ -12238,39 +11823,107 @@
         <v>31</v>
       </c>
       <c r="W13" s="14" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="X13" s="212">
         <v>45973</v>
       </c>
     </row>
-    <row r="14" spans="2:24" ht="14.25" thickBot="1">
-      <c r="B14" s="10">
+    <row r="14" spans="2:24" ht="40.5">
+      <c r="C14" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="211" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="79" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14" s="230" t="s">
+        <v>31</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="V14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="X14" s="212">
+        <v>46058</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B15" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="231"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -12308,27 +11961,27 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="160" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="160" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6" s="160"/>
     </row>
     <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="83" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="91"/>
       <c r="E7" s="84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="20.25" customHeight="1" thickTop="1">
@@ -12336,10 +11989,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="92" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="163" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -12357,7 +12010,7 @@
     </row>
     <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="161" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="90"/>
       <c r="D12" s="90"/>
@@ -12365,13 +12018,13 @@
     <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="162"/>
       <c r="C13" s="167" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="91" t="s">
+      <c r="E13" s="84" t="s">
         <v>140</v>
-      </c>
-      <c r="E13" s="84" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="14.25" thickTop="1">
@@ -12379,10 +12032,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="92" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="169" t="s">
         <v>153</v>
-      </c>
-      <c r="E14" s="169" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -12393,7 +12046,7 @@
         <v>23</v>
       </c>
       <c r="E15" s="79" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:5">
@@ -12404,7 +12057,7 @@
         <v>24</v>
       </c>
       <c r="E16" s="79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -12415,7 +12068,7 @@
         <v>25</v>
       </c>
       <c r="E17" s="79" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -12426,7 +12079,7 @@
         <v>26</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -12434,10 +12087,10 @@
         <v>5</v>
       </c>
       <c r="D19" s="93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E19" s="79" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -12445,10 +12098,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="93" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="14.25" thickBot="1">
@@ -12458,18 +12111,18 @@
     </row>
     <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="160" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="167" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="91" t="s">
+      <c r="E25" s="84" t="s">
         <v>140</v>
-      </c>
-      <c r="E25" s="84" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="30.75" customHeight="1" thickTop="1">
@@ -12477,10 +12130,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" s="169" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="120" customHeight="1">
@@ -12488,10 +12141,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="93" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E27" s="95" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="81" customHeight="1">
@@ -12499,10 +12152,10 @@
         <v>2</v>
       </c>
       <c r="D28" s="93" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E28" s="95" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="45" customHeight="1">
@@ -12510,10 +12163,10 @@
         <v>3</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E29" s="95" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="16.5" customHeight="1">
@@ -12521,10 +12174,10 @@
         <v>4</v>
       </c>
       <c r="D30" s="93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="79" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="16.5" customHeight="1">
@@ -12532,10 +12185,10 @@
         <v>5</v>
       </c>
       <c r="D31" s="93" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E31" s="79" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -12555,19 +12208,19 @@
     </row>
     <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="160" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="251"/>
-      <c r="D38" s="252"/>
+      <c r="C38" s="252"/>
+      <c r="D38" s="253"/>
       <c r="E38" s="119" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="253"/>
-      <c r="D39" s="254"/>
+      <c r="C39" s="254"/>
+      <c r="D39" s="255"/>
       <c r="E39" s="6" t="s">
         <v>125</v>
       </c>
@@ -12607,44 +12260,44 @@
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="D2" s="261" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263"/>
+      <c r="C2" s="257"/>
+      <c r="D2" s="262" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="257" t="s">
+      <c r="B3" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="264" t="s">
-        <v>282</v>
-      </c>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266"/>
+      <c r="C3" s="259"/>
+      <c r="D3" s="265" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" s="266"/>
+      <c r="F3" s="266"/>
+      <c r="G3" s="266"/>
+      <c r="H3" s="267"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="260"/>
-      <c r="D4" s="267" t="str">
+      <c r="C4" s="261"/>
+      <c r="D4" s="268" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_H_LEAUNF-CSTD-1-00-A-C0.c</v>
       </c>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="270"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
@@ -12653,70 +12306,70 @@
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="255" t="s">
+      <c r="B6" s="256" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="256"/>
-      <c r="D6" s="270" t="str">
+      <c r="C6" s="257"/>
+      <c r="D6" s="271" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>H_LEAUNF</v>
       </c>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="272"/>
+      <c r="E6" s="272"/>
+      <c r="F6" s="272"/>
+      <c r="G6" s="272"/>
+      <c r="H6" s="273"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="257" t="s">
+      <c r="B7" s="258" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="258"/>
-      <c r="D7" s="273">
+      <c r="C7" s="259"/>
+      <c r="D7" s="274">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="274"/>
-      <c r="F7" s="274"/>
-      <c r="G7" s="274"/>
-      <c r="H7" s="275"/>
+      <c r="E7" s="275"/>
+      <c r="F7" s="275"/>
+      <c r="G7" s="275"/>
+      <c r="H7" s="276"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="257" t="s">
+      <c r="B8" s="258" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="258"/>
-      <c r="D8" s="273" t="str">
+      <c r="C8" s="259"/>
+      <c r="D8" s="274" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_H_LEAUNF_MTRX</v>
       </c>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="275"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="275"/>
+      <c r="H8" s="276"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="257" t="s">
+      <c r="B9" s="258" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="258"/>
-      <c r="D9" s="276" t="s">
-        <v>219</v>
-      </c>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="278"/>
+      <c r="C9" s="259"/>
+      <c r="D9" s="277" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="278"/>
+      <c r="F9" s="278"/>
+      <c r="G9" s="278"/>
+      <c r="H9" s="279"/>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="259" t="s">
+      <c r="B10" s="260" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="260"/>
-      <c r="D10" s="279"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="281"/>
+      <c r="C10" s="261"/>
+      <c r="D10" s="280"/>
+      <c r="E10" s="281"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="281"/>
+      <c r="H10" s="282"/>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="12" spans="2:14" ht="14.25" thickBot="1">
@@ -12759,13 +12412,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D13" s="118" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="118" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F13" s="55" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
@@ -13722,10 +13375,10 @@
   <sheetData>
     <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="14.25" thickBot="1">
@@ -13733,19 +13386,19 @@
         <v>34</v>
       </c>
       <c r="C3" s="110" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="111" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="110" t="s">
-        <v>204</v>
-      </c>
-      <c r="E3" s="111" t="s">
-        <v>205</v>
-      </c>
       <c r="F3" s="195" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G3" s="192" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="H3" s="49"/>
       <c r="I3" s="49"/>
@@ -13757,13 +13410,13 @@
         <v>34</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Q3" s="191" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="R3" s="192" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
@@ -13771,7 +13424,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="184" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D4" s="184"/>
       <c r="E4" s="185"/>
@@ -13787,10 +13440,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="190" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="Q4" s="190" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="R4" s="146"/>
     </row>
@@ -14346,10 +13999,10 @@
     </row>
     <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O32" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="14.25" thickBot="1">
@@ -14357,31 +14010,31 @@
         <v>34</v>
       </c>
       <c r="C33" s="110" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D33" s="110" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E33" s="111" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F33" s="192" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G33" s="192" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="O33" s="151" t="s">
         <v>34</v>
       </c>
       <c r="P33" s="191" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Q33" s="191" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="R33" s="192" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
@@ -14389,25 +14042,25 @@
         <v>0</v>
       </c>
       <c r="C34" s="184" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D34" s="184"/>
       <c r="E34" s="185"/>
       <c r="F34" s="194" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G34" s="197"/>
       <c r="O34" s="193">
         <v>0</v>
       </c>
       <c r="P34" s="190" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="Q34" s="190" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="R34" s="194" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="2:18" ht="14.25" thickTop="1">
@@ -15037,7 +14690,7 @@
         <v>55</v>
       </c>
       <c r="J2" s="108" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="K2" s="107" t="s">
         <v>56</v>
@@ -15078,10 +14731,10 @@
     </row>
     <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="27" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D4" s="120">
         <v>0</v>
@@ -15102,7 +14755,7 @@
         <v>132</v>
       </c>
       <c r="J4" s="122" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="K4" s="121" t="s">
         <v>132</v>
@@ -17695,7 +17348,7 @@
       <c r="B2" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="282" t="s">
+      <c r="C2" s="283" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="61">
@@ -17794,7 +17447,7 @@
       <c r="AI2" s="61">
         <v>0</v>
       </c>
-      <c r="AJ2" s="284" t="s">
+      <c r="AJ2" s="285" t="s">
         <v>51</v>
       </c>
     </row>
@@ -17803,7 +17456,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="283"/>
+      <c r="C3" s="284"/>
       <c r="D3" s="135" t="s">
         <v>61</v>
       </c>
@@ -17895,21 +17548,21 @@
         <v>62</v>
       </c>
       <c r="AH3" s="209" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AI3" s="209" t="s">
-        <v>234</v>
-      </c>
-      <c r="AJ3" s="285"/>
+        <v>222</v>
+      </c>
+      <c r="AJ3" s="286"/>
       <c r="AR3" s="97" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="286" t="s">
+      <c r="A4" s="287" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="287"/>
+      <c r="B4" s="288"/>
       <c r="C4" s="199"/>
       <c r="D4" s="199"/>
       <c r="E4" s="199"/>
@@ -17954,8 +17607,8 @@
       <c r="AW4" s="87"/>
     </row>
     <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="288"/>
-      <c r="B5" s="289"/>
+      <c r="A5" s="289"/>
+      <c r="B5" s="290"/>
       <c r="C5" s="200"/>
       <c r="D5" s="200"/>
       <c r="E5" s="200"/>
@@ -18250,7 +17903,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="26" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -46451,7 +46104,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B56:Q87"/>
+  <dimension ref="B75:Q87"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
@@ -46464,468 +46117,9 @@
     <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="56" spans="2:17" ht="15" thickBot="1">
-      <c r="B56" s="28" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="57" spans="2:17" ht="15" thickBot="1">
-      <c r="B57" s="101" t="s">
-        <v>164</v>
-      </c>
-      <c r="C57" s="294" t="s">
-        <v>230</v>
-      </c>
-      <c r="D57" s="295"/>
-      <c r="E57" s="295"/>
-      <c r="F57" s="295"/>
-      <c r="G57" s="295"/>
-      <c r="H57" s="295"/>
-      <c r="I57" s="295"/>
-      <c r="J57" s="296"/>
-      <c r="K57" s="179"/>
-      <c r="L57" s="179"/>
-      <c r="M57" s="182"/>
-      <c r="N57" s="180"/>
-      <c r="O57" s="180"/>
-      <c r="P57" s="180"/>
-      <c r="Q57" s="181"/>
-    </row>
-    <row r="58" spans="2:17">
-      <c r="B58" s="73"/>
-      <c r="C58" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="36"/>
-      <c r="M58" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="N58" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" s="47"/>
-      <c r="P58" s="47"/>
-      <c r="Q58" s="48"/>
-    </row>
-    <row r="59" spans="2:17">
-      <c r="B59" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" s="293" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" s="291"/>
-      <c r="E59" s="291"/>
-      <c r="F59" s="291"/>
-      <c r="G59" s="291"/>
-      <c r="H59" s="291"/>
-      <c r="I59" s="291"/>
-      <c r="J59" s="292"/>
-      <c r="K59" s="201" t="s">
-        <v>235</v>
-      </c>
-      <c r="L59" s="78"/>
-      <c r="M59" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="N59" s="206" t="s">
-        <v>23</v>
-      </c>
-      <c r="O59" s="202" t="s">
-        <v>24</v>
-      </c>
-      <c r="P59" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q59" s="146" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60" spans="2:17">
-      <c r="B60" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="D60" s="173" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="G60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="H60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="I60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="J60" s="173" t="s">
-        <v>178</v>
-      </c>
-      <c r="K60" s="145" t="s">
-        <v>221</v>
-      </c>
-      <c r="L60" s="145" t="s">
-        <v>221</v>
-      </c>
-      <c r="M60" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="N60" s="207"/>
-      <c r="O60" s="205"/>
-      <c r="P60" s="82"/>
-      <c r="Q60" s="146"/>
-    </row>
-    <row r="61" spans="2:17" ht="27">
-      <c r="B61" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C61" s="290" t="s">
-        <v>168</v>
-      </c>
-      <c r="D61" s="291"/>
-      <c r="E61" s="291"/>
-      <c r="F61" s="291"/>
-      <c r="G61" s="291"/>
-      <c r="H61" s="291"/>
-      <c r="I61" s="291"/>
-      <c r="J61" s="292"/>
-      <c r="K61" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="L61" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="M61" s="33"/>
-      <c r="N61" s="207"/>
-      <c r="O61" s="205"/>
-      <c r="P61" s="82"/>
-      <c r="Q61" s="146"/>
-    </row>
-    <row r="62" spans="2:17" ht="136.5">
-      <c r="B62" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="174" t="s">
-        <v>169</v>
-      </c>
-      <c r="D62" s="174" t="s">
-        <v>62</v>
-      </c>
-      <c r="E62" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="F62" s="174" t="s">
-        <v>171</v>
-      </c>
-      <c r="G62" s="174" t="s">
-        <v>172</v>
-      </c>
-      <c r="H62" s="174" t="s">
-        <v>173</v>
-      </c>
-      <c r="I62" s="174" t="s">
-        <v>174</v>
-      </c>
-      <c r="J62" s="174" t="s">
-        <v>175</v>
-      </c>
-      <c r="K62" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="L62" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="M62" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="N62" s="207"/>
-      <c r="O62" s="205"/>
-      <c r="P62" s="82"/>
-      <c r="Q62" s="146"/>
-    </row>
-    <row r="63" spans="2:17" ht="41.25" thickBot="1">
-      <c r="B63" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="D63" s="175" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="F63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="G63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="H63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="I63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="J63" s="175" t="s">
-        <v>177</v>
-      </c>
-      <c r="K63" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="L63" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="M63" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="N63" s="208"/>
-      <c r="O63" s="203" t="s">
-        <v>240</v>
-      </c>
-      <c r="P63" s="80"/>
-      <c r="Q63" s="147"/>
-    </row>
-    <row r="64" spans="2:17" ht="14.25" thickTop="1">
-      <c r="B64" s="77" t="s">
-        <v>245</v>
-      </c>
-      <c r="C64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="D64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="E64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="F64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="G64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="H64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="I64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="J64" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="L64" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="M64" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="N64" s="176"/>
-      <c r="O64" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="P64" s="43"/>
-      <c r="Q64" s="148"/>
-    </row>
-    <row r="65" spans="2:17">
-      <c r="B65" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="D65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="E65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="F65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="G65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="H65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="I65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="J65" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="K65" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="L65" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="M65" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="N65" s="177"/>
-      <c r="O65" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="P65" s="44"/>
-      <c r="Q65" s="149"/>
-    </row>
-    <row r="66" spans="2:17">
-      <c r="B66" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="D66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="E66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="F66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="G66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="H66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="I66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="J66" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="K66" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="L66" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="M66" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="N66" s="177"/>
-      <c r="O66" s="64" t="s">
-        <v>241</v>
-      </c>
-      <c r="P66" s="44"/>
-      <c r="Q66" s="149"/>
-    </row>
-    <row r="67" spans="2:17">
-      <c r="B67" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="C67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="D67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="E67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="F67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="G67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="H67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="I67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="J67" s="177" t="s">
-        <v>176</v>
-      </c>
-      <c r="K67" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="L67" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="M67" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="N67" s="177"/>
-      <c r="O67" s="64" t="s">
-        <v>241</v>
-      </c>
-      <c r="P67" s="44"/>
-      <c r="Q67" s="149"/>
-    </row>
-    <row r="68" spans="2:17" ht="14.25" thickBot="1">
-      <c r="B68" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="D68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="E68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="F68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="G68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="H68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="I68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="J68" s="178" t="s">
-        <v>176</v>
-      </c>
-      <c r="K68" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="L68" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="M68" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="N68" s="178"/>
-      <c r="O68" s="204" t="s">
-        <v>241</v>
-      </c>
-      <c r="P68" s="45"/>
-      <c r="Q68" s="150"/>
-    </row>
     <row r="75" spans="2:17" ht="15" thickBot="1">
       <c r="B75" s="28" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="2:17" ht="15" thickBot="1">
@@ -46933,7 +46127,7 @@
         <v>129</v>
       </c>
       <c r="C76" s="294" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D76" s="295"/>
       <c r="E76" s="295"/>
@@ -46953,7 +46147,7 @@
     <row r="77" spans="2:17">
       <c r="B77" s="73"/>
       <c r="C77" s="35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D77" s="35"/>
       <c r="E77" s="35"/>
@@ -46978,22 +46172,22 @@
       <c r="B78" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="293" t="s">
-        <v>185</v>
-      </c>
-      <c r="D78" s="291"/>
-      <c r="E78" s="291"/>
-      <c r="F78" s="291"/>
-      <c r="G78" s="291"/>
-      <c r="H78" s="291"/>
-      <c r="I78" s="291"/>
-      <c r="J78" s="292"/>
+      <c r="C78" s="297" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" s="292"/>
+      <c r="E78" s="292"/>
+      <c r="F78" s="292"/>
+      <c r="G78" s="292"/>
+      <c r="H78" s="292"/>
+      <c r="I78" s="292"/>
+      <c r="J78" s="293"/>
       <c r="K78" s="201" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="L78" s="78"/>
       <c r="M78" s="32" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="N78" s="206" t="s">
         <v>23</v>
@@ -47037,10 +46231,10 @@
         <v>133</v>
       </c>
       <c r="K79" s="145" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L79" s="145" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="M79" s="32" t="s">
         <v>48</v>
@@ -47054,21 +46248,21 @@
       <c r="B80" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="290" t="s">
+      <c r="C80" s="291" t="s">
         <v>35</v>
       </c>
-      <c r="D80" s="291"/>
-      <c r="E80" s="291"/>
-      <c r="F80" s="291"/>
-      <c r="G80" s="291"/>
-      <c r="H80" s="291"/>
-      <c r="I80" s="291"/>
-      <c r="J80" s="292"/>
+      <c r="D80" s="292"/>
+      <c r="E80" s="292"/>
+      <c r="F80" s="292"/>
+      <c r="G80" s="292"/>
+      <c r="H80" s="292"/>
+      <c r="I80" s="292"/>
+      <c r="J80" s="293"/>
       <c r="K80" s="29" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="L80" s="29" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="M80" s="33"/>
       <c r="N80" s="207"/>
@@ -47081,34 +46275,34 @@
         <v>28</v>
       </c>
       <c r="C81" s="174" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D81" s="174" t="s">
         <v>62</v>
       </c>
       <c r="E81" s="174" t="s">
+        <v>165</v>
+      </c>
+      <c r="F81" s="174" t="s">
+        <v>166</v>
+      </c>
+      <c r="G81" s="174" t="s">
+        <v>167</v>
+      </c>
+      <c r="H81" s="174" t="s">
+        <v>168</v>
+      </c>
+      <c r="I81" s="174" t="s">
+        <v>169</v>
+      </c>
+      <c r="J81" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="F81" s="174" t="s">
-        <v>171</v>
-      </c>
-      <c r="G81" s="174" t="s">
-        <v>172</v>
-      </c>
-      <c r="H81" s="174" t="s">
-        <v>173</v>
-      </c>
-      <c r="I81" s="174" t="s">
-        <v>174</v>
-      </c>
-      <c r="J81" s="174" t="s">
-        <v>175</v>
-      </c>
       <c r="K81" s="29" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="L81" s="29" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="M81" s="32" t="s">
         <v>29</v>
@@ -47123,277 +46317,274 @@
         <v>30</v>
       </c>
       <c r="C82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D82" s="175" t="s">
         <v>133</v>
       </c>
       <c r="E82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J82" s="175" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L82" s="30" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="M82" s="34" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="N82" s="208"/>
       <c r="O82" s="203" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="P82" s="80"/>
       <c r="Q82" s="147"/>
     </row>
     <row r="83" spans="2:17" ht="14.25" thickTop="1">
       <c r="B83" s="77" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J83" s="176" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K83" s="38" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="L83" s="38" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="M83" s="39" t="s">
         <v>110</v>
       </c>
       <c r="N83" s="176"/>
       <c r="O83" s="137" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P83" s="43"/>
       <c r="Q83" s="148"/>
     </row>
     <row r="84" spans="2:17">
       <c r="B84" s="23" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J84" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K84" s="37" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="L84" s="37" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="M84" s="40" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="N84" s="177"/>
       <c r="O84" s="64" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="P84" s="44"/>
       <c r="Q84" s="149"/>
     </row>
     <row r="85" spans="2:17">
       <c r="B85" s="23" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J85" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K85" s="37" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="L85" s="37" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="M85" s="40" t="s">
         <v>32</v>
       </c>
       <c r="N85" s="177"/>
       <c r="O85" s="64" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P85" s="44"/>
       <c r="Q85" s="149"/>
     </row>
     <row r="86" spans="2:17">
       <c r="B86" s="23" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J86" s="177" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K86" s="37" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="L86" s="37" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="M86" s="40" t="s">
         <v>32</v>
       </c>
       <c r="N86" s="177"/>
       <c r="O86" s="64" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P86" s="44"/>
       <c r="Q86" s="149"/>
     </row>
     <row r="87" spans="2:17" ht="14.25" thickBot="1">
       <c r="B87" s="24" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J87" s="178" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K87" s="41" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="L87" s="41" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="M87" s="42" t="s">
         <v>32</v>
       </c>
       <c r="N87" s="178"/>
       <c r="O87" s="204" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P87" s="45"/>
       <c r="Q87" s="150"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
     <mergeCell ref="C80:J80"/>
-    <mergeCell ref="C59:J59"/>
-    <mergeCell ref="C61:J61"/>
-    <mergeCell ref="C57:J57"/>
     <mergeCell ref="C76:J76"/>
     <mergeCell ref="C78:J78"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C57 C76" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
@@ -47575,10 +46766,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D16" s="95" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="27">
@@ -47589,7 +46780,7 @@
         <v>94</v>
       </c>
       <c r="D17" s="95" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="67.5">
@@ -47600,7 +46791,7 @@
         <v>94</v>
       </c>
       <c r="D18" s="95" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="40.5">
@@ -47611,7 +46802,7 @@
         <v>108</v>
       </c>
       <c r="D19" s="95" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="64.5" customHeight="1">
@@ -47622,7 +46813,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="95" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="66.75" customHeight="1">
@@ -47630,10 +46821,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="95" t="s">
         <v>206</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="27">
@@ -47641,10 +46832,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="93" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D22" s="95" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="27">
@@ -47652,10 +46843,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="93" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D23" s="95" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="94.5">
@@ -47663,10 +46854,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="93" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="D24" s="95" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="2:4">
